--- a/day8/mydata.xlsx
+++ b/day8/mydata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\smitp\Desktop\Infolabz\day7\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{16745B8E-7EFD-4026-94C0-532587AD4AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C00ED5-E05D-47C9-B659-9197485C0A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E64598A1-13FD-46DA-88BD-77DADEA87494}"/>
   </bookViews>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
